--- a/chapter1.xlsx
+++ b/chapter1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\資訊安全\網頁前後測\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0 NCUT 勤益資料\勤益課程\資訊安全\網頁前後測\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FAE9AE-8F90-429F-88DB-B852DFAD758C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C43187-2021-4C25-8504-2FA5A0DD0B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-6190" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="7560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
@@ -1872,7 +1872,7 @@
         <v>173</v>
       </c>
       <c r="F39" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="30.9" x14ac:dyDescent="0.4">
